--- a/tests/testthat/testdata/files_unparsed/election_templates/prop_template.xlsx
+++ b/tests/testthat/testdata/files_unparsed/election_templates/prop_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\STAT\01_Post\Graf\eCH-0157_testfiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\STAT\01_Post\Graf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C07B502-EE3E-45B4-977E-2F29D31CAE3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC849E2-2C04-4505-BF05-C52ADEF3F06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="75" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="15" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="142">
   <si>
     <t>nachname</t>
   </si>
@@ -85,36 +85,144 @@
     <t>Frauke</t>
   </si>
   <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>Alpstrasse</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>8464</t>
+  </si>
+  <si>
+    <t>Rheinau</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>04.01</t>
+  </si>
+  <si>
+    <t>Die Mitte</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>Heimgartner-Müller</t>
   </si>
   <si>
     <t>Maria</t>
   </si>
   <si>
+    <t>Diozänin</t>
+  </si>
+  <si>
+    <t>Herbstgasse</t>
+  </si>
+  <si>
+    <t>02.01</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Sozialdemokratische Partei Rheinau</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Müller</t>
   </si>
   <si>
     <t>Anna</t>
   </si>
   <si>
+    <t>Softwareentwicklerin</t>
+  </si>
+  <si>
+    <t>Moltkestrasse</t>
+  </si>
+  <si>
+    <t>02.02</t>
+  </si>
+  <si>
+    <t>ja</t>
+  </si>
+  <si>
     <t>Weber</t>
   </si>
   <si>
     <t>Markus</t>
   </si>
   <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Krankenpfleger</t>
+  </si>
+  <si>
+    <t>Zürcherstrasse</t>
+  </si>
+  <si>
+    <t>29a</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>02.03</t>
+  </si>
+  <si>
     <t>Schmid</t>
   </si>
   <si>
     <t>Leda</t>
   </si>
   <si>
+    <t>Grafikdesignerin EFZ</t>
+  </si>
+  <si>
+    <t>EFZ</t>
+  </si>
+  <si>
+    <t>Kaiserstrasse</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>02.04</t>
+  </si>
+  <si>
     <t>Tobias</t>
   </si>
   <si>
     <t>Hoffmann</t>
   </si>
   <si>
+    <t>Sekundarlehrperson</t>
+  </si>
+  <si>
+    <t>Bahnhofstrasse</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>02.05</t>
+  </si>
+  <si>
     <t>Lüthi</t>
   </si>
   <si>
@@ -124,400 +232,220 @@
     <t>Sophie</t>
   </si>
   <si>
+    <t>Medizinische Praxisassistentin MPA</t>
+  </si>
+  <si>
+    <t>Römerstrasse</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>02.06</t>
+  </si>
+  <si>
     <t>Schneider</t>
   </si>
   <si>
     <t>Fabian</t>
   </si>
   <si>
+    <t>Architekt ETH</t>
+  </si>
+  <si>
+    <t>ETH</t>
+  </si>
+  <si>
+    <t>Stadthausstrasse</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>02.07</t>
+  </si>
+  <si>
     <t>Roth</t>
   </si>
   <si>
     <t>Karin</t>
   </si>
   <si>
+    <t>Journalistin, Reitlehrerin</t>
+  </si>
+  <si>
+    <t>Schlossstrasse</t>
+  </si>
+  <si>
+    <t>02.08</t>
+  </si>
+  <si>
     <t>Mayer</t>
   </si>
   <si>
     <t>Timo</t>
   </si>
   <si>
+    <t>Elektronikingenieur, Mühlenbauer</t>
+  </si>
+  <si>
+    <t>Industriestrasse</t>
+  </si>
+  <si>
+    <t>02.09</t>
+  </si>
+  <si>
     <t>Brunner</t>
   </si>
   <si>
     <t>Lea</t>
   </si>
   <si>
+    <t>Unternehmensberaterin, M.Sc. Econ</t>
+  </si>
+  <si>
+    <t>M.Sc. Econ</t>
+  </si>
+  <si>
+    <t>Bäckerstrasse</t>
+  </si>
+  <si>
+    <t>22b</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>02.10</t>
+  </si>
+  <si>
     <t>Märki</t>
   </si>
   <si>
     <t>Adolf</t>
   </si>
   <si>
+    <t>Pensioniert</t>
+  </si>
+  <si>
+    <t>Dorfplatz</t>
+  </si>
+  <si>
+    <t>03.01</t>
+  </si>
+  <si>
+    <t>FDP</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
     <t>Heimgartner</t>
   </si>
   <si>
     <t>Raffael</t>
   </si>
   <si>
+    <t>Malermeister</t>
+  </si>
+  <si>
+    <t>Ämtlerstrasse</t>
+  </si>
+  <si>
+    <t>01.01</t>
+  </si>
+  <si>
+    <t>SVP</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Schweizerische Volkspartei SVP</t>
+  </si>
+  <si>
     <t>Berner</t>
   </si>
   <si>
     <t>Marionne</t>
   </si>
   <si>
+    <t>Krankenpflegerin</t>
+  </si>
+  <si>
+    <t>01.02</t>
+  </si>
+  <si>
     <t>Frank</t>
   </si>
   <si>
+    <t>Rasenmähervertreter</t>
+  </si>
+  <si>
+    <t>Holzerhauserstrasse</t>
+  </si>
+  <si>
+    <t>01.03</t>
+  </si>
+  <si>
     <t>Bernhart</t>
   </si>
   <si>
     <t>Benni</t>
   </si>
   <si>
+    <t>Forstwart</t>
+  </si>
+  <si>
+    <t>01.04</t>
+  </si>
+  <si>
     <t>Rösseler</t>
   </si>
   <si>
     <t>Annegret</t>
   </si>
   <si>
+    <t>Hausfrau</t>
+  </si>
+  <si>
+    <t>Marktgasse</t>
+  </si>
+  <si>
+    <t>01.05</t>
+  </si>
+  <si>
     <t>Albrecht</t>
   </si>
   <si>
     <t>Christina</t>
   </si>
   <si>
+    <t>Sekundarlehrerin, Vorsteherin "Rheinau tanzt"</t>
+  </si>
+  <si>
+    <t>Oberdorf</t>
+  </si>
+  <si>
+    <t>01.06</t>
+  </si>
+  <si>
     <t>Gurbic</t>
   </si>
   <si>
     <t>Zoljuban</t>
   </si>
   <si>
-    <t>1962-05-06</t>
-  </si>
-  <si>
-    <t>1961-09-30</t>
-  </si>
-  <si>
-    <t>1987-03-12</t>
-  </si>
-  <si>
-    <t>1991-07-03</t>
-  </si>
-  <si>
-    <t>1960-11-18</t>
-  </si>
-  <si>
-    <t>1983-04-05</t>
-  </si>
-  <si>
-    <t>1997-12-03</t>
-  </si>
-  <si>
-    <t>1990-08-19</t>
-  </si>
-  <si>
-    <t>1956-01-22</t>
-  </si>
-  <si>
-    <t>1999-05-08</t>
-  </si>
-  <si>
-    <t>1996-02-05</t>
-  </si>
-  <si>
-    <t>1947-11-14</t>
-  </si>
-  <si>
-    <t>1960-01-30</t>
-  </si>
-  <si>
-    <t>2000-07-09</t>
-  </si>
-  <si>
-    <t>1973-06-15</t>
-  </si>
-  <si>
-    <t>1987-03-13</t>
-  </si>
-  <si>
-    <t>1965-12-10</t>
-  </si>
-  <si>
-    <t>1994-02-09</t>
-  </si>
-  <si>
-    <t>1954-08-13</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Alpstrasse</t>
-  </si>
-  <si>
-    <t>Herbstgasse</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>Moltkestrasse</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>Zürcherstrasse</t>
-  </si>
-  <si>
-    <t>29a</t>
-  </si>
-  <si>
-    <t>Kaiserstrasse</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Bahnhofstrasse</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Römerstrasse</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>Stadthausstrasse</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Schlossstrasse</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Industriestrasse</t>
-  </si>
-  <si>
-    <t>Bäckerstrasse</t>
-  </si>
-  <si>
-    <t>22b</t>
-  </si>
-  <si>
-    <t>Dorfplatz</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Ämtlerstrasse</t>
-  </si>
-  <si>
-    <t>Holzerhauserstrasse</t>
-  </si>
-  <si>
-    <t>Marktgasse</t>
-  </si>
-  <si>
-    <t>Oberdorf</t>
+    <t>Pensionierter Mathematiker</t>
   </si>
   <si>
     <t>Im Schöntal</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Rheinau</t>
-  </si>
-  <si>
-    <t>8464</t>
-  </si>
-  <si>
-    <t>Die Mitte</t>
-  </si>
-  <si>
-    <t>SP</t>
-  </si>
-  <si>
-    <t>FDP</t>
-  </si>
-  <si>
-    <t>SVP</t>
-  </si>
-  <si>
-    <t>Sozialdemokratische Partei Rheinau</t>
-  </si>
-  <si>
-    <t>Schweizerische Volkspartei SVP</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Diozänin</t>
-  </si>
-  <si>
-    <t>Softwareentwicklerin</t>
-  </si>
-  <si>
-    <t>Krankenpfleger</t>
-  </si>
-  <si>
-    <t>Grafikdesignerin EFZ</t>
-  </si>
-  <si>
-    <t>Sekundarlehrperson</t>
-  </si>
-  <si>
-    <t>Medizinische Praxisassistentin MPA</t>
-  </si>
-  <si>
-    <t>Architekt ETH</t>
-  </si>
-  <si>
-    <t>Journalistin, Reitlehrerin</t>
-  </si>
-  <si>
-    <t>Elektronikingenieur, Mühlenbauer</t>
-  </si>
-  <si>
-    <t>Unternehmensberaterin, M.Sc. Econ</t>
-  </si>
-  <si>
-    <t>Pensioniert</t>
-  </si>
-  <si>
-    <t>Malermeister</t>
-  </si>
-  <si>
-    <t>Krankenpflegerin</t>
-  </si>
-  <si>
-    <t>Rasenmähervertreter</t>
-  </si>
-  <si>
-    <t>Forstwart</t>
-  </si>
-  <si>
-    <t>Hausfrau</t>
-  </si>
-  <si>
-    <t>Sekundarlehrerin, Vorsteherin "Rheinau tanzt"</t>
-  </si>
-  <si>
-    <t>Pensionierter Mathematiker</t>
-  </si>
-  <si>
-    <t>EFZ</t>
-  </si>
-  <si>
-    <t>ETH</t>
-  </si>
-  <si>
-    <t>M.Sc. Econ</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>04.01</t>
-  </si>
-  <si>
-    <t>02.01</t>
-  </si>
-  <si>
-    <t>02.02</t>
-  </si>
-  <si>
-    <t>02.03</t>
-  </si>
-  <si>
-    <t>02.04</t>
-  </si>
-  <si>
-    <t>02.05</t>
-  </si>
-  <si>
-    <t>02.06</t>
-  </si>
-  <si>
-    <t>02.07</t>
-  </si>
-  <si>
-    <t>02.08</t>
-  </si>
-  <si>
-    <t>02.09</t>
-  </si>
-  <si>
-    <t>02.10</t>
-  </si>
-  <si>
-    <t>03.01</t>
-  </si>
-  <si>
-    <t>01.01</t>
-  </si>
-  <si>
-    <t>01.02</t>
-  </si>
-  <si>
-    <t>01.03</t>
-  </si>
-  <si>
-    <t>01.04</t>
-  </si>
-  <si>
-    <t>01.05</t>
-  </si>
-  <si>
-    <t>01.06</t>
-  </si>
-  <si>
     <t>01.07</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>w</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>ja</t>
   </si>
 </sst>
 </file>
@@ -561,11 +489,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -963,553 +892,553 @@
       <c r="C2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
-        <v>57</v>
+      <c r="D2" s="2">
+        <v>22772</v>
       </c>
       <c r="E2" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I2" t="s">
-        <v>76</v>
+        <v>22</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
       </c>
       <c r="J2" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>140</v>
+        <v>27</v>
       </c>
       <c r="O2" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="P2" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="R2" t="s">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="S2" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2">
+        <v>22554</v>
+      </c>
+      <c r="E3" t="s">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" t="s">
-        <v>163</v>
-      </c>
       <c r="F3" t="s">
-        <v>115</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" t="s">
-        <v>80</v>
+        <v>34</v>
+      </c>
+      <c r="I3">
+        <v>96</v>
       </c>
       <c r="J3" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="O3" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="Q3" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="R3" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="S3" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="2">
+        <v>31848</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I4" t="s">
-        <v>82</v>
-      </c>
-      <c r="J4" t="s">
-        <v>107</v>
-      </c>
-      <c r="K4" t="s">
-        <v>106</v>
-      </c>
-      <c r="L4" t="s">
-        <v>76</v>
-      </c>
       <c r="M4" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="N4" t="s">
-        <v>165</v>
+        <v>45</v>
       </c>
       <c r="O4" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="P4" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="Q4" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="R4" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="S4" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
+        <v>47</v>
+      </c>
+      <c r="D5" s="2">
+        <v>33422</v>
       </c>
       <c r="E5" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="F5" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="I5" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="J5" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="M5" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="O5" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="P5" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="Q5" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="R5" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="S5" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="D6" s="2">
+        <v>22238</v>
       </c>
       <c r="E6" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="G6" t="s">
-        <v>133</v>
+        <v>57</v>
       </c>
       <c r="H6" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" t="s">
-        <v>86</v>
+        <v>58</v>
+      </c>
+      <c r="I6">
+        <v>15</v>
       </c>
       <c r="J6" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K6" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="M6" t="s">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="O6" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="P6" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="Q6" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="R6" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="S6" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
         <v>62</v>
       </c>
+      <c r="D7" s="2">
+        <v>30411</v>
+      </c>
       <c r="E7" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="H7" t="s">
-        <v>87</v>
-      </c>
-      <c r="I7" t="s">
-        <v>88</v>
+        <v>64</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
       </c>
       <c r="J7" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K7" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="M7" t="s">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="O7" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="P7" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="Q7" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="R7" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="S7" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>63</v>
+        <v>69</v>
+      </c>
+      <c r="D8" s="2">
+        <v>35767</v>
       </c>
       <c r="E8" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H8" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" t="s">
-        <v>90</v>
+        <v>71</v>
+      </c>
+      <c r="I8">
+        <v>55</v>
       </c>
       <c r="J8" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K8" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="M8" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="O8" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="P8" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="Q8" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="R8" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="S8" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
+        <v>75</v>
+      </c>
+      <c r="D9" s="2">
+        <v>33104</v>
       </c>
       <c r="E9" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="F9" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="H9" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" t="s">
-        <v>92</v>
+        <v>78</v>
+      </c>
+      <c r="I9">
+        <v>8</v>
       </c>
       <c r="J9" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K9" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L9" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="M9" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="O9" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="P9" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="R9" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="S9" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="2">
+        <v>20476</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10">
+        <v>14</v>
+      </c>
+      <c r="J10" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>79</v>
+      </c>
+      <c r="M10" t="s">
+        <v>86</v>
+      </c>
+      <c r="O10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
+      <c r="P10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" t="s">
-        <v>163</v>
-      </c>
-      <c r="F10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" t="s">
-        <v>94</v>
-      </c>
-      <c r="J10" t="s">
-        <v>107</v>
-      </c>
-      <c r="K10" t="s">
-        <v>106</v>
-      </c>
-      <c r="L10" t="s">
-        <v>92</v>
-      </c>
-      <c r="M10" t="s">
-        <v>148</v>
-      </c>
-      <c r="O10" t="s">
-        <v>109</v>
-      </c>
-      <c r="P10" t="s">
-        <v>137</v>
-      </c>
       <c r="Q10" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="R10" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="S10" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="2">
+        <v>36288</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H11" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>30</v>
+      </c>
+      <c r="M11" t="s">
+        <v>91</v>
+      </c>
+      <c r="O11" t="s">
+        <v>36</v>
+      </c>
+      <c r="P11" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>36</v>
+      </c>
+      <c r="R11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" t="s">
+      <c r="S11" t="s">
         <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" t="s">
-        <v>164</v>
-      </c>
-      <c r="F11" t="s">
-        <v>123</v>
-      </c>
-      <c r="H11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I11" t="s">
-        <v>86</v>
-      </c>
-      <c r="J11" t="s">
-        <v>107</v>
-      </c>
-      <c r="K11" t="s">
-        <v>106</v>
-      </c>
-      <c r="L11" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" t="s">
-        <v>149</v>
-      </c>
-      <c r="O11" t="s">
-        <v>109</v>
-      </c>
-      <c r="P11" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>109</v>
-      </c>
-      <c r="R11" t="s">
-        <v>112</v>
-      </c>
-      <c r="S11" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>67</v>
+        <v>93</v>
+      </c>
+      <c r="D12" s="2">
+        <v>35100</v>
       </c>
       <c r="E12" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="G12" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="H12" t="s">
         <v>96</v>
@@ -1518,614 +1447,614 @@
         <v>97</v>
       </c>
       <c r="J12" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K12" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="M12" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="O12" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="P12" t="s">
-        <v>137</v>
+        <v>37</v>
       </c>
       <c r="Q12" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="R12" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="S12" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>68</v>
+        <v>101</v>
+      </c>
+      <c r="D13" s="2">
+        <v>17485</v>
       </c>
       <c r="E13" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="F13" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="H13" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+      <c r="I13">
+        <v>7</v>
       </c>
       <c r="J13" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
+        <v>104</v>
+      </c>
+      <c r="O13" t="s">
+        <v>105</v>
+      </c>
+      <c r="P13" t="s">
         <v>106</v>
       </c>
-      <c r="L13" t="s">
-        <v>77</v>
-      </c>
-      <c r="M13" t="s">
-        <v>151</v>
-      </c>
-      <c r="O13" t="s">
-        <v>110</v>
-      </c>
-      <c r="P13" t="s">
-        <v>138</v>
-      </c>
       <c r="Q13" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="R13" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="S13" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="B14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="2">
+        <v>21945</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" t="s">
+        <v>110</v>
+      </c>
+      <c r="I14">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
+        <v>111</v>
+      </c>
+      <c r="N14" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" t="s">
-        <v>164</v>
-      </c>
-      <c r="F14" t="s">
-        <v>126</v>
-      </c>
-      <c r="H14" t="s">
-        <v>100</v>
-      </c>
-      <c r="I14" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" t="s">
-        <v>107</v>
-      </c>
-      <c r="K14" t="s">
-        <v>106</v>
-      </c>
-      <c r="L14" t="s">
-        <v>77</v>
-      </c>
-      <c r="M14" t="s">
-        <v>152</v>
-      </c>
-      <c r="N14" t="s">
-        <v>165</v>
-      </c>
       <c r="O14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P14" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S14" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="B15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" t="s">
+        <v>108</v>
+      </c>
+      <c r="D15" s="2">
+        <v>21945</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>109</v>
+      </c>
+      <c r="H15" t="s">
+        <v>110</v>
+      </c>
+      <c r="I15">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>23</v>
+      </c>
+      <c r="M15" t="s">
+        <v>111</v>
+      </c>
+      <c r="N15" t="s">
         <v>45</v>
       </c>
-      <c r="C15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" t="s">
-        <v>164</v>
-      </c>
-      <c r="F15" t="s">
-        <v>126</v>
-      </c>
-      <c r="H15" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" t="s">
-        <v>107</v>
-      </c>
-      <c r="K15" t="s">
-        <v>106</v>
-      </c>
-      <c r="L15" t="s">
-        <v>76</v>
-      </c>
-      <c r="M15" t="s">
-        <v>152</v>
-      </c>
-      <c r="N15" t="s">
-        <v>165</v>
-      </c>
       <c r="O15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P15" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S15" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" t="s">
-        <v>70</v>
+        <v>116</v>
+      </c>
+      <c r="D16" s="2">
+        <v>36716</v>
       </c>
       <c r="E16" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="J16" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K16" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L16" t="s">
-        <v>159</v>
+        <v>52</v>
       </c>
       <c r="M16" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="N16" t="s">
-        <v>165</v>
+        <v>45</v>
       </c>
       <c r="O16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P16" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S16" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" t="s">
-        <v>70</v>
+        <v>116</v>
+      </c>
+      <c r="D17" s="2">
+        <v>36716</v>
       </c>
       <c r="E17" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="J17" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K17" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L17" t="s">
-        <v>160</v>
+        <v>59</v>
       </c>
       <c r="M17" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="N17" t="s">
-        <v>165</v>
+        <v>45</v>
       </c>
       <c r="O17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P17" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S17" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="2">
+        <v>26830</v>
+      </c>
+      <c r="E18" t="s">
         <v>48</v>
       </c>
-      <c r="C18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" t="s">
-        <v>164</v>
-      </c>
       <c r="F18" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
-      </c>
-      <c r="I18" t="s">
-        <v>86</v>
+        <v>121</v>
+      </c>
+      <c r="I18">
+        <v>15</v>
       </c>
       <c r="J18" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K18" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L18" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="N18" t="s">
-        <v>165</v>
+        <v>45</v>
       </c>
       <c r="O18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P18" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S18" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="2">
+        <v>26830</v>
+      </c>
+      <c r="E19" t="s">
         <v>48</v>
       </c>
-      <c r="C19" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E19" t="s">
-        <v>164</v>
-      </c>
       <c r="F19" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="H19" t="s">
-        <v>101</v>
-      </c>
-      <c r="I19" t="s">
-        <v>86</v>
+        <v>121</v>
+      </c>
+      <c r="I19">
+        <v>15</v>
       </c>
       <c r="J19" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K19" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L19" t="s">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="M19" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="N19" t="s">
-        <v>165</v>
+        <v>45</v>
       </c>
       <c r="O19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P19" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S19" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" t="s">
-        <v>72</v>
+        <v>124</v>
+      </c>
+      <c r="D20" s="2">
+        <v>31849</v>
       </c>
       <c r="E20" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="F20" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J20" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K20" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L20" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="M20" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="O20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P20" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S20" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" t="s">
-        <v>73</v>
+        <v>41</v>
+      </c>
+      <c r="D21" s="2">
+        <v>24086</v>
       </c>
       <c r="E21" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="F21" t="s">
+        <v>129</v>
+      </c>
+      <c r="H21" t="s">
         <v>130</v>
       </c>
-      <c r="H21" t="s">
-        <v>102</v>
-      </c>
-      <c r="I21" t="s">
-        <v>76</v>
+      <c r="I21">
+        <v>2</v>
       </c>
       <c r="J21" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K21" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="M21" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="O21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P21" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S21" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" t="s">
-        <v>74</v>
+        <v>133</v>
+      </c>
+      <c r="D22" s="2">
+        <v>34374</v>
       </c>
       <c r="E22" t="s">
-        <v>163</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H22" t="s">
-        <v>103</v>
-      </c>
-      <c r="I22" t="s">
-        <v>86</v>
+        <v>135</v>
+      </c>
+      <c r="I22">
+        <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K22" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L22" t="s">
-        <v>88</v>
+        <v>30</v>
       </c>
       <c r="M22" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="O22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P22" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S22" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" t="s">
-        <v>75</v>
+        <v>138</v>
+      </c>
+      <c r="D23" s="2">
+        <v>19949</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="F23" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H23" t="s">
-        <v>104</v>
-      </c>
-      <c r="I23" t="s">
-        <v>105</v>
+        <v>140</v>
+      </c>
+      <c r="I23">
+        <v>5</v>
       </c>
       <c r="J23" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="K23" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="L23" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="M23" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="O23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P23" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="Q23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S23" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
